--- a/clases/data/II-1123_03_Ejemplos y ejercicios resueltos.xlsx
+++ b/clases/data/II-1123_03_Ejemplos y ejercicios resueltos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve\Dropbox\Sitio personal\stevenggoni.github.io\clases\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2E3942-CB00-44C2-A378-0D6480540F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1884851-9999-434D-8ADB-B2D653FFABDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{A1BEAFC4-0D6D-41FE-A28D-35D4F4DAC3E7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{A1BEAFC4-0D6D-41FE-A28D-35D4F4DAC3E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Ejemplo 01" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,6 @@
     <t>W</t>
   </si>
   <si>
-    <t>https://homepage.divms.uiowa.edu/~mbognar/applets/wilcoxon-signed-rank.html</t>
-  </si>
-  <si>
     <t>P(W &lt;= w)</t>
   </si>
   <si>
@@ -147,12 +144,6 @@
     <t>Wilcoxon</t>
   </si>
   <si>
-    <t>https://homepage.divms.uiowa.edu/~mbognar/applets/wilcoxon-rank-sum.html</t>
-  </si>
-  <si>
-    <t>https://homepage.divms.uiowa.edu/~mbognar/applets/mw.html</t>
-  </si>
-  <si>
     <t>P(W1&gt;=99)</t>
   </si>
   <si>
@@ -169,6 +160,15 @@
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>https://mabognar.github.io/apps/wilcoxon-signed-rank.html</t>
+  </si>
+  <si>
+    <t>https://mabognar.github.io/apps/wilcoxon-rank-sum.html</t>
+  </si>
+  <si>
+    <t>https://mabognar.github.io/apps/mw.html</t>
   </si>
 </sst>
 </file>
@@ -177,7 +177,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="173" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -303,16 +303,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1216,23 +1216,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>178792</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>12092</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>300078</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>156729</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>60214</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>140306</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>155464</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>32386</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
+        <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAE9C31B-E2B1-6EC7-DDCD-4F0F1E70DC54}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AB4780D-8E26-F2AD-5A29-9DE5B9EF5C6B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1248,8 +1248,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11583944" y="2745353"/>
-          <a:ext cx="5111558" cy="3231625"/>
+          <a:off x="6180730" y="2707772"/>
+          <a:ext cx="5379886" cy="2608918"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1260,23 +1260,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>566427</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>103863</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>395660</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>119768</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>51208</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>174099</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>165653</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>59930</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
+        <xdr:cNvPr id="8" name="Picture 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DCA2EAE-B847-E2D5-0718-21A271FDF1DB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7D37D6A-6735-06D9-9780-6AB9CAA1ECBC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1292,8 +1292,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6430514" y="2886820"/>
-          <a:ext cx="4977807" cy="3224253"/>
+          <a:off x="11800812" y="2670811"/>
+          <a:ext cx="5609232" cy="2673423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2020,7 +2020,7 @@
     <col min="6" max="6" width="6.88671875" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="6"/>
     <col min="8" max="8" width="19.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
@@ -2494,13 +2494,13 @@
         <v>5</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L7" s="15">
         <v>4.8649999999999999E-2</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.3">
@@ -2874,11 +2874,8 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G22">
     <sortCondition ref="F2:F22"/>
   </sortState>
-  <hyperlinks>
-    <hyperlink ref="M7" r:id="rId1" xr:uid="{A1D576C4-874D-434B-8024-BD578149A151}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2904,14 +2901,14 @@
   <sheetData>
     <row r="1" spans="2:21" x14ac:dyDescent="0.3">
       <c r="L1" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N1" s="17"/>
       <c r="O1" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P1" s="17"/>
       <c r="Q1" s="17"/>
@@ -2919,39 +2916,39 @@
     </row>
     <row r="2" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2">
         <f>+SUMIF($H$3:$H$22,L2,$J$3:$J$22)</f>
         <v>99</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P2" s="2">
         <f>+COUNTIF($H$3:$H$22,L2)</f>
         <v>10</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R2" s="2">
         <f>+N2-(P2*(P2+1)/2)</f>
@@ -2966,7 +2963,7 @@
         <v>3261</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="2">
         <v>3187</v>
@@ -2976,24 +2973,24 @@
         <v>1</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N3" s="2">
         <f>+SUMIF($H$3:$H$22,L3,$J$3:$J$22)</f>
         <v>111</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P3" s="2">
         <f>+COUNTIF($H$3:$H$22,L3)</f>
         <v>10</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R3" s="2">
         <f>+N3-(P3*(P3+1)/2)</f>
@@ -3008,7 +3005,7 @@
         <v>3187</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I4" s="2">
         <v>3190</v>
@@ -3018,14 +3015,14 @@
         <v>2</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N4" s="17"/>
       <c r="O4" s="17" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
@@ -3039,7 +3036,7 @@
         <v>3209</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2">
         <v>3195</v>
@@ -3050,20 +3047,20 @@
       </c>
       <c r="L5" s="17"/>
       <c r="M5" s="18">
-        <v>0.68474000000000002</v>
+        <v>0.34211000000000003</v>
       </c>
       <c r="N5" s="18"/>
       <c r="O5" s="18">
-        <v>0.68740000000000001</v>
+        <v>0.34211000000000003</v>
       </c>
       <c r="P5" s="18"/>
       <c r="Q5" s="18"/>
       <c r="R5" s="18"/>
       <c r="T5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.3">
@@ -3074,7 +3071,7 @@
         <v>3212</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6" s="2">
         <v>3204</v>
@@ -3095,10 +3092,10 @@
       <c r="Q6" s="17"/>
       <c r="R6" s="17"/>
       <c r="T6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U6" s="14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
@@ -3109,7 +3106,7 @@
         <v>3258</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2">
         <v>3209</v>
@@ -3120,13 +3117,13 @@
       </c>
       <c r="L7" s="17"/>
       <c r="M7" s="18">
-        <f>+M5</f>
-        <v>0.68474000000000002</v>
+        <f>+M5*2</f>
+        <v>0.68422000000000005</v>
       </c>
       <c r="N7" s="18"/>
       <c r="O7" s="18">
-        <f>+O5</f>
-        <v>0.68740000000000001</v>
+        <f>+O5*2</f>
+        <v>0.68422000000000005</v>
       </c>
       <c r="P7" s="18"/>
       <c r="Q7" s="18"/>
@@ -3140,7 +3137,7 @@
         <v>3248</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2">
         <v>3212</v>
@@ -3149,15 +3146,15 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="L8" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
+      <c r="L8" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
@@ -3167,7 +3164,7 @@
         <v>3215</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I9" s="2">
         <v>3215</v>
@@ -3176,13 +3173,13 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
@@ -3192,7 +3189,7 @@
         <v>3226</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I10" s="2">
         <v>3217</v>
@@ -3210,7 +3207,7 @@
         <v>3240</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" s="2">
         <v>3225</v>
@@ -3228,7 +3225,7 @@
         <v>3234</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I12" s="2">
         <v>3226</v>
@@ -3240,7 +3237,7 @@
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="H13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I13" s="2">
         <v>3229</v>
@@ -3252,7 +3249,7 @@
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.3">
       <c r="H14" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2">
         <v>3234</v>
@@ -3264,7 +3261,7 @@
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.3">
       <c r="H15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I15" s="2">
         <v>3238</v>
@@ -3276,7 +3273,7 @@
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.3">
       <c r="H16" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I16" s="2">
         <v>3240</v>
@@ -3288,7 +3285,7 @@
     </row>
     <row r="17" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I17" s="2">
         <v>3241</v>
@@ -3300,7 +3297,7 @@
     </row>
     <row r="18" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I18" s="2">
         <v>3246</v>
@@ -3312,7 +3309,7 @@
     </row>
     <row r="19" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H19" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I19" s="2">
         <v>3248</v>
@@ -3324,7 +3321,7 @@
     </row>
     <row r="20" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H20" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I20" s="2">
         <v>3254</v>
@@ -3336,7 +3333,7 @@
     </row>
     <row r="21" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H21" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I21" s="2">
         <v>3258</v>
@@ -3348,7 +3345,7 @@
     </row>
     <row r="22" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H22" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I22" s="2">
         <v>3261</v>
@@ -3377,12 +3374,8 @@
     <mergeCell ref="O4:R4"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="U5" r:id="rId1" xr:uid="{4DD6FF20-5367-48C1-A47A-9B232119B056}"/>
-    <hyperlink ref="U6" r:id="rId2" xr:uid="{7055E5BF-B87C-494E-8CAC-31FF7B49139B}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3396,327 +3389,327 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>41</v>
+      <c r="A2" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B2" s="12">
         <v>84.3457261058402</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
-        <v>41</v>
+      <c r="A3" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B3" s="12">
         <v>57.661027088761301</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
-        <v>41</v>
+      <c r="A4" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B4" s="12">
         <v>132.90548678067401</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
-        <v>41</v>
+      <c r="A5" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B5" s="12">
         <v>3.1577359108311902</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
-        <v>41</v>
+      <c r="A6" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B6" s="12">
         <v>5.6210976094007501</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
-        <v>41</v>
+      <c r="A7" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B7" s="12">
         <v>31.650121637771001</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
-        <v>41</v>
+      <c r="A8" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B8" s="12">
         <v>31.4227292215297</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
-        <v>41</v>
+      <c r="A9" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B9" s="12">
         <v>14.526680391281801</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
-        <v>41</v>
+      <c r="A10" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B10" s="12">
         <v>272.62364643297002</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
-        <v>41</v>
+      <c r="A11" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B11" s="12">
         <v>2.9153447082572601</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
-        <v>41</v>
+      <c r="A12" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B12" s="12">
         <v>100.48300576907501</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
-        <v>41</v>
+      <c r="A13" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B13" s="12">
         <v>48.0214727659774</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
-        <v>41</v>
+      <c r="A14" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B14" s="12">
         <v>28.101362753659501</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
-        <v>41</v>
+      <c r="A15" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B15" s="12">
         <v>37.711783106713398</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
-        <v>41</v>
+      <c r="A16" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B16" s="12">
         <v>18.828404089435899</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="19" t="s">
-        <v>41</v>
+      <c r="A17" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B17" s="12">
         <v>84.978612973810499</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="19" t="s">
-        <v>41</v>
+      <c r="A18" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B18" s="12">
         <v>156.32035396153</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
-        <v>41</v>
+      <c r="A19" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B19" s="12">
         <v>47.876041633655497</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="19" t="s">
-        <v>41</v>
+      <c r="A20" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B20" s="12">
         <v>59.093483537435503</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="19" t="s">
-        <v>41</v>
+      <c r="A21" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B21" s="12">
         <v>404.10117113724999</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
-        <v>42</v>
+      <c r="A22" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B22" s="12">
         <v>168.62994622675501</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
-        <v>42</v>
+      <c r="A23" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B23" s="12">
         <v>193.17424221986801</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="19" t="s">
-        <v>42</v>
+      <c r="A24" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B24" s="12">
         <v>297.05515880361401</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="19" t="s">
-        <v>42</v>
+      <c r="A25" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B25" s="12">
         <v>269.60889714861202</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="19" t="s">
-        <v>42</v>
+      <c r="A26" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B26" s="12">
         <v>233.70579685175699</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="19" t="s">
-        <v>42</v>
+      <c r="A27" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B27" s="12">
         <v>321.17046861160298</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="19" t="s">
-        <v>42</v>
+      <c r="A28" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B28" s="12">
         <v>299.34857374239499</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="19" t="s">
-        <v>42</v>
+      <c r="A29" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B29" s="12">
         <v>314.13050937904501</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="19" t="s">
-        <v>42</v>
+      <c r="A30" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B30" s="12">
         <v>6.3535487922951903</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="19" t="s">
-        <v>42</v>
+      <c r="A31" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B31" s="12">
         <v>119.569938257337</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="19" t="s">
-        <v>42</v>
+      <c r="A32" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B32" s="12">
         <v>433.56794909563098</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="19" t="s">
-        <v>42</v>
+      <c r="A33" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B33" s="12">
         <v>101.32314572110801</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="19" t="s">
-        <v>42</v>
+      <c r="A34" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B34" s="12">
         <v>51.911563466014499</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="19" t="s">
-        <v>42</v>
+      <c r="A35" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B35" s="12">
         <v>519.37842329306102</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="19" t="s">
-        <v>42</v>
+      <c r="A36" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B36" s="12">
         <v>245.805146350505</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="19" t="s">
-        <v>42</v>
+      <c r="A37" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B37" s="12">
         <v>158.136351770701</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="19" t="s">
-        <v>42</v>
+      <c r="A38" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B38" s="12">
         <v>125.856015551835</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="19" t="s">
-        <v>42</v>
+      <c r="A39" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B39" s="12">
         <v>250.92820058956801</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="19" t="s">
-        <v>42</v>
+      <c r="A40" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B40" s="12">
         <v>117.736928444356</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="19" t="s">
-        <v>42</v>
+      <c r="A41" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B41" s="12">
         <v>225.85800676982501</v>
